--- a/Bauhalle_Zeitplan_woechentlich.xlsx
+++ b/Bauhalle_Zeitplan_woechentlich.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hueppim\Documents\Github\BauhallenUhr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8211F95-B6F5-45CA-A1F4-3E244E69D91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BFCC56-6618-4D98-8266-963B8AE01CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6165" yWindow="3225" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Zeitplan wöchentlich" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="82">
   <si>
     <t>Bauhalle Zeitplan wöchentlich</t>
   </si>
@@ -285,13 +285,17 @@
 Dazu darf die Zeit fürs Schema nicht 40h betragen, sondern eher 10h oder max. 15h.
 Beim Schema sollte ich mehr mit vorgefertigten Komponenten und Symbolen/ Footprints arbeiten, dadurch spare ich eine Menge Zeit.
 Ich sollte für die IPA dann auch meinen "Perfektionismus" ablegen.</t>
+  </si>
+  <si>
+    <t>Hier habe ich zwischendurch am WoodMoisture gearbeitet, daher hatte ich nicht immer an der BauhallenUhr gearbeitet.
+Deswegen konnte ich den Termin für die Besprechung des PCBs nicht einhalten. Ich habe das aber 2 Tage vorher so kommuniziert.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,6 +395,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="15">
@@ -682,7 +692,7 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -757,6 +767,49 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" xfId="10" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="5" xfId="10" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -805,32 +858,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -839,7 +870,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1121,11 +1152,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1269,194 +1300,194 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="73" t="s">
+      <c r="D6" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="74" t="s">
+      <c r="H6" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="77"/>
+      <c r="P6" s="77"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="78" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="70"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="70"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="74"/>
+      <c r="A7" s="77"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="77"/>
+      <c r="R7" s="77"/>
+      <c r="S7" s="78"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="70"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
-      <c r="O8" s="70"/>
-      <c r="P8" s="70"/>
-      <c r="Q8" s="70"/>
-      <c r="R8" s="70"/>
-      <c r="S8" s="74"/>
+      <c r="A8" s="77"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="77"/>
+      <c r="N8" s="77"/>
+      <c r="O8" s="77"/>
+      <c r="P8" s="77"/>
+      <c r="Q8" s="77"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="78"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="70"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="70"/>
-      <c r="N9" s="70"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="70"/>
-      <c r="Q9" s="70"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="74"/>
+      <c r="A9" s="77"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="77"/>
+      <c r="P9" s="77"/>
+      <c r="Q9" s="77"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="78"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="70"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="70"/>
-      <c r="K10" s="70"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="70"/>
-      <c r="P10" s="70"/>
-      <c r="Q10" s="70"/>
-      <c r="R10" s="70"/>
-      <c r="S10" s="74"/>
+      <c r="A10" s="77"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="77"/>
+      <c r="N10" s="77"/>
+      <c r="O10" s="77"/>
+      <c r="P10" s="77"/>
+      <c r="Q10" s="77"/>
+      <c r="R10" s="77"/>
+      <c r="S10" s="78"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="70"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="70"/>
-      <c r="N11" s="70"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="70"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="74"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="77"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="77"/>
+      <c r="S11" s="78"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="70"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="70"/>
-      <c r="K12" s="70"/>
-      <c r="L12" s="70"/>
-      <c r="M12" s="70"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="70"/>
-      <c r="P12" s="70"/>
-      <c r="Q12" s="70"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="74"/>
+      <c r="A12" s="77"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="77"/>
+      <c r="N12" s="77"/>
+      <c r="O12" s="77"/>
+      <c r="P12" s="77"/>
+      <c r="Q12" s="77"/>
+      <c r="R12" s="77"/>
+      <c r="S12" s="78"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="70"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70"/>
-      <c r="L13" s="70"/>
-      <c r="M13" s="70"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="70"/>
-      <c r="Q13" s="70"/>
-      <c r="R13" s="70"/>
-      <c r="S13" s="74"/>
+      <c r="A13" s="77"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="77"/>
+      <c r="N13" s="77"/>
+      <c r="O13" s="77"/>
+      <c r="P13" s="77"/>
+      <c r="Q13" s="77"/>
+      <c r="R13" s="77"/>
+      <c r="S13" s="78"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
@@ -1652,26 +1683,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="B6:B13"/>
+    <mergeCell ref="C6:C13"/>
+    <mergeCell ref="D6:D13"/>
+    <mergeCell ref="E6:E13"/>
+    <mergeCell ref="F6:F13"/>
+    <mergeCell ref="G6:G13"/>
+    <mergeCell ref="H6:H13"/>
+    <mergeCell ref="I6:I13"/>
+    <mergeCell ref="J6:J13"/>
+    <mergeCell ref="K6:K13"/>
+    <mergeCell ref="L6:L13"/>
+    <mergeCell ref="M6:M13"/>
+    <mergeCell ref="N6:N13"/>
     <mergeCell ref="O6:O13"/>
     <mergeCell ref="P6:P13"/>
     <mergeCell ref="Q6:Q13"/>
     <mergeCell ref="R6:R13"/>
     <mergeCell ref="S6:S13"/>
-    <mergeCell ref="J6:J13"/>
-    <mergeCell ref="K6:K13"/>
-    <mergeCell ref="L6:L13"/>
-    <mergeCell ref="M6:M13"/>
-    <mergeCell ref="N6:N13"/>
-    <mergeCell ref="E6:E13"/>
-    <mergeCell ref="F6:F13"/>
-    <mergeCell ref="G6:G13"/>
-    <mergeCell ref="H6:H13"/>
-    <mergeCell ref="I6:I13"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="B6:B13"/>
-    <mergeCell ref="C6:C13"/>
-    <mergeCell ref="D6:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1680,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -1692,11 +1723,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="29"/>
@@ -2275,476 +2306,717 @@
       <c r="A28" s="29">
         <v>25</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
+      <c r="B28" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="38">
+        <v>46239</v>
+      </c>
+      <c r="D28" s="30">
+        <v>32</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="30">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="29">
         <v>26</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
+      <c r="B29" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="38">
+        <v>46240</v>
+      </c>
+      <c r="D29" s="30">
+        <v>32</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="30">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="29">
+        <v>27</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="38">
+        <v>46240</v>
+      </c>
+      <c r="D30" s="30">
+        <v>32</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="30">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="29">
+        <v>28</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="38">
+        <v>46241</v>
+      </c>
+      <c r="D31" s="30">
+        <v>32</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="29">
+        <v>29</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="38">
+        <v>46251</v>
+      </c>
+      <c r="D32" s="30">
+        <v>34</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="30">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="29">
+        <v>30</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="38">
+        <v>46252</v>
+      </c>
+      <c r="D33" s="30">
+        <v>34</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="30">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="29">
+        <v>31</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="38">
+        <v>46253</v>
+      </c>
+      <c r="D34" s="30">
+        <v>34</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="30">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="29">
+        <v>32</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="38">
+        <v>46255</v>
+      </c>
+      <c r="D35" s="30">
+        <v>34</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="29">
+        <v>33</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="38">
+        <v>46258</v>
+      </c>
+      <c r="D36" s="30">
+        <v>35</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="30">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="29">
+        <v>34</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="38">
+        <v>46259</v>
+      </c>
+      <c r="D37" s="30">
+        <v>35</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="62" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="62"/>
-      <c r="C32" s="29" t="s">
+      <c r="B40" s="50"/>
+      <c r="C40" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D40" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E32" s="29" t="s">
+      <c r="E40" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F40" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="G32" s="29" t="s">
+      <c r="G40" s="29" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="69" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="69"/>
-      <c r="C33" s="32">
+      <c r="B41" s="51"/>
+      <c r="C41" s="32">
         <v>16</v>
       </c>
-      <c r="D33" s="28">
-        <f>SUMIFS($G$4:$G$1003,$F$4:$F$1003,$A33,$E$4:$E$1003,"Thermostat")</f>
+      <c r="D41" s="28">
+        <f>SUMIFS($G$4:$G$1011,$F$4:$F$1011,$A41,$E$4:$E$1011,"Thermostat")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="33">
-        <f>IF($C33&lt;$D33, $C33/$D33*9+1, $D33/$C33*9+1)</f>
+      <c r="E41" s="33">
+        <f>IF($C41&lt;$D41, $C41/$D41*9+1, $D41/$C41*9+1)</f>
         <v>1</v>
       </c>
-      <c r="F33" s="35"/>
-      <c r="G33" s="41" t="s">
+      <c r="F41" s="35"/>
+      <c r="G41" s="41" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="67" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="67"/>
-      <c r="C34" s="17">
+      <c r="B42" s="48"/>
+      <c r="C42" s="17">
         <v>8</v>
       </c>
-      <c r="D34" s="4">
-        <f>SUMIFS($G$4:$G$1003,$F$4:$F$1003,$A34,$E$4:$E$1003,"Thermostat")</f>
+      <c r="D42" s="4">
+        <f>SUMIFS($G$4:$G$1011,$F$4:$F$1011,$A42,$E$4:$E$1011,"Thermostat")</f>
         <v>8.5</v>
       </c>
-      <c r="E34" s="34">
-        <f>IF($C34&lt;$D34, $C34/$D34*9+1, $D34/$C34*9+1)</f>
+      <c r="E42" s="34">
+        <f>IF($C42&lt;$D42, $C42/$D42*9+1, $D42/$C42*9+1)</f>
         <v>9.4705882352941178</v>
       </c>
-      <c r="F34" s="35"/>
-      <c r="G34" s="40" t="s">
+      <c r="F42" s="35"/>
+      <c r="G42" s="40" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="67" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="67"/>
-      <c r="C35" s="17">
+      <c r="B43" s="48"/>
+      <c r="C43" s="17">
         <v>8</v>
       </c>
-      <c r="D35" s="4">
-        <f>SUMIFS($G$4:$G$1003,$F$4:$F$1003,$A35,$E$4:$E$1003,"Thermostat")</f>
+      <c r="D43" s="4">
+        <f>SUMIFS($G$4:$G$1011,$F$4:$F$1011,$A43,$E$4:$E$1011,"Thermostat")</f>
         <v>1</v>
       </c>
-      <c r="E35" s="34">
-        <f>IF($C35&lt;$D35, $C35/$D35*9+1, $D35/$C35*9+1)</f>
+      <c r="E43" s="34">
+        <f>IF($C43&lt;$D43, $C43/$D43*9+1, $D43/$C43*9+1)</f>
         <v>2.125</v>
       </c>
-      <c r="F35" s="35"/>
-      <c r="G35" s="41" t="s">
+      <c r="F43" s="35"/>
+      <c r="G43" s="41" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="65" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="66"/>
-      <c r="C36" s="17">
+      <c r="B44" s="47"/>
+      <c r="C44" s="17">
         <v>4</v>
       </c>
-      <c r="D36" s="4">
-        <f>SUMIFS($G$4:$G$1003,$F$4:$F$1003,$A36,$E$4:$E$1003,"Thermostat")</f>
+      <c r="D44" s="4">
+        <f>SUMIFS($G$4:$G$1011,$F$4:$F$1011,$A44,$E$4:$E$1011,"Thermostat")</f>
         <v>15.5</v>
       </c>
-      <c r="E36" s="34">
-        <f>IF($C36&lt;$D36, $C36/$D36*9+1, $D36/$C36*9+1)</f>
+      <c r="E44" s="34">
+        <f>IF($C44&lt;$D44, $C44/$D44*9+1, $D44/$C44*9+1)</f>
         <v>3.32258064516129</v>
       </c>
-      <c r="F36" s="35"/>
-      <c r="G36" s="41" t="s">
+      <c r="F44" s="35"/>
+      <c r="G44" s="41" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="67" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="67"/>
-      <c r="C37" s="17">
-        <f>SUM($C33:$C36)</f>
+      <c r="B45" s="48"/>
+      <c r="C45" s="17">
+        <f>SUM($C41:$C44)</f>
         <v>36</v>
       </c>
-      <c r="D37" s="4">
-        <f>SUM(D33:D36)</f>
+      <c r="D45" s="4">
+        <f>SUM(D41:D44)</f>
         <v>25</v>
       </c>
-      <c r="E37" s="34">
-        <f>IF($C37&lt;$D37, $C37/$D37*9+1, $D37/$C37*9+1)</f>
+      <c r="E45" s="34">
+        <f>IF($C45&lt;$D45, $C45/$D45*9+1, $D45/$C45*9+1)</f>
         <v>7.25</v>
       </c>
-      <c r="F37" s="35"/>
-      <c r="G37" s="42" t="s">
+      <c r="F45" s="35"/>
+      <c r="G45" s="42" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="62" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B39" s="62"/>
-      <c r="C39" s="29" t="s">
+      <c r="B47" s="50"/>
+      <c r="C47" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D47" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E47" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="F39" s="29" t="s">
+      <c r="F47" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="G39" s="29" t="s">
+      <c r="G47" s="29" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="63" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="14">
+      <c r="B48" s="53"/>
+      <c r="C48" s="14">
         <v>8</v>
       </c>
-      <c r="D40" s="4">
-        <f t="shared" ref="D40:D47" si="0">SUMIFS($G$4:$G$1003,$F$4:$F$1003,$A40,$E$4:$E$1003,"BauhallenUhr")</f>
+      <c r="D48" s="4">
+        <f t="shared" ref="D48:D55" si="0">SUMIFS($G$4:$G$1011,$F$4:$F$1011,$A48,$E$4:$E$1011,"BauhallenUhr")</f>
         <v>19</v>
       </c>
-      <c r="E40" s="34">
-        <f t="shared" ref="E40:E48" si="1">IF($C40&lt;$D40, $C40/$D40*9+1, $D40/$C40*9+1)</f>
+      <c r="E48" s="34">
+        <f t="shared" ref="E48:E56" si="1">IF($C48&lt;$D48, $C48/$D48*9+1, $D48/$C48*9+1)</f>
         <v>4.7894736842105257</v>
       </c>
-      <c r="F40" s="35"/>
-      <c r="G40" s="43" t="s">
+      <c r="F48" s="35"/>
+      <c r="G48" s="43" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="63" t="s">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="B41" s="64"/>
-      <c r="C41" s="14">
+      <c r="B49" s="53"/>
+      <c r="C49" s="14">
         <v>8</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D49" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E49" s="34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F41" s="34"/>
-      <c r="G41" s="4"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="63" t="s">
+      <c r="F49" s="34"/>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="B42" s="64"/>
-      <c r="C42" s="14">
+      <c r="B50" s="53"/>
+      <c r="C50" s="14">
         <v>8</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D50" s="4">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="E42" s="34">
+      <c r="E50" s="34">
         <f t="shared" si="1"/>
         <v>1.5625</v>
       </c>
-      <c r="F42" s="34"/>
-      <c r="G42" s="43" t="s">
+      <c r="F50" s="34"/>
+      <c r="G50" s="43" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="63" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="B43" s="64"/>
-      <c r="C43" s="14">
+      <c r="B51" s="53"/>
+      <c r="C51" s="14">
         <v>40</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D51" s="4">
         <f t="shared" si="0"/>
-        <v>49.5</v>
-      </c>
-      <c r="E43" s="34">
+        <v>58</v>
+      </c>
+      <c r="E51" s="34">
         <f t="shared" si="1"/>
-        <v>8.2727272727272734</v>
-      </c>
-      <c r="F43" s="35"/>
-      <c r="G43" s="44" t="s">
+        <v>7.2068965517241388</v>
+      </c>
+      <c r="F51" s="35"/>
+      <c r="G51" s="44" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="63" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="64"/>
-      <c r="C44" s="14">
+      <c r="B52" s="53"/>
+      <c r="C52" s="14">
         <v>40</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D52" s="4">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="E52" s="34">
+        <f t="shared" si="1"/>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F52" s="34"/>
+      <c r="G52" s="44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="53"/>
+      <c r="C53" s="14">
+        <v>20</v>
+      </c>
+      <c r="D53" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E44" s="34">
+      <c r="E53" s="34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F44" s="34"/>
-      <c r="G44" s="4"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45" s="64"/>
-      <c r="C45" s="14">
-        <v>20</v>
-      </c>
-      <c r="D45" s="4">
+      <c r="F53" s="34"/>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" s="53"/>
+      <c r="C54" s="14">
+        <v>15</v>
+      </c>
+      <c r="D54" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E45" s="34">
+      <c r="E54" s="34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F45" s="34"/>
-      <c r="G45" s="4"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="64"/>
-      <c r="C46" s="14">
+      <c r="F54" s="34"/>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B55" s="53"/>
+      <c r="C55" s="14">
         <v>15</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D55" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E46" s="34">
+      <c r="E55" s="34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F46" s="34"/>
-      <c r="G46" s="4"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="63" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="64"/>
-      <c r="C47" s="14">
-        <v>15</v>
-      </c>
-      <c r="D47" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E47" s="34">
+      <c r="F55" s="33"/>
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" s="53"/>
+      <c r="C56" s="14">
+        <f>SUM($C48:$C55)</f>
+        <v>154</v>
+      </c>
+      <c r="D56" s="4">
+        <f>SUM(D48:D55)</f>
+        <v>127.5</v>
+      </c>
+      <c r="E56" s="34">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="F47" s="33"/>
-      <c r="G47" s="4"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="64"/>
-      <c r="C48" s="14">
-        <f>SUM($C40:$C47)</f>
-        <v>154</v>
-      </c>
-      <c r="D48" s="4">
-        <f>SUM(D40:D47)</f>
-        <v>69</v>
-      </c>
-      <c r="E48" s="34">
-        <f t="shared" si="1"/>
-        <v>5.0324675324675319</v>
-      </c>
-      <c r="F48" s="33"/>
-      <c r="G48" s="4"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="19"/>
-      <c r="B50" s="4" t="s">
+        <v>8.4512987012987004</v>
+      </c>
+      <c r="F56" s="33"/>
+      <c r="G56" s="4"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="19"/>
+      <c r="B58" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="36"/>
-      <c r="B51" s="4" t="s">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="36"/>
+      <c r="B59" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="45" t="s">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="45" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="43" t="s">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="B54" s="58" t="s">
+      <c r="B62" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="58"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="43" t="s">
+      <c r="C62" s="73"/>
+      <c r="D62" s="73"/>
+      <c r="E62" s="73"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="73"/>
+      <c r="H62" s="73"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="B55" s="59" t="s">
+      <c r="B63" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="C55" s="60"/>
-      <c r="D55" s="60"/>
-      <c r="E55" s="60"/>
-      <c r="F55" s="60"/>
-      <c r="G55" s="60"/>
-      <c r="H55" s="61"/>
-    </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="46" t="s">
+      <c r="C63" s="75"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
+      <c r="F63" s="75"/>
+      <c r="G63" s="75"/>
+      <c r="H63" s="76"/>
+    </row>
+    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="B57" s="49" t="s">
+      <c r="B65" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="C57" s="50"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="50"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="50"/>
-      <c r="I57" s="50"/>
-      <c r="J57" s="51"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="47"/>
-      <c r="B58" s="52"/>
-      <c r="C58" s="53"/>
-      <c r="D58" s="53"/>
-      <c r="E58" s="53"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="53"/>
-      <c r="H58" s="53"/>
-      <c r="I58" s="53"/>
-      <c r="J58" s="54"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="47"/>
-      <c r="B59" s="52"/>
-      <c r="C59" s="53"/>
-      <c r="D59" s="53"/>
-      <c r="E59" s="53"/>
-      <c r="F59" s="53"/>
-      <c r="G59" s="53"/>
-      <c r="H59" s="53"/>
-      <c r="I59" s="53"/>
-      <c r="J59" s="54"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="48"/>
-      <c r="B60" s="55"/>
-      <c r="C60" s="56"/>
-      <c r="D60" s="56"/>
-      <c r="E60" s="56"/>
-      <c r="F60" s="56"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="56"/>
-      <c r="I60" s="56"/>
-      <c r="J60" s="57"/>
+      <c r="C65" s="65"/>
+      <c r="D65" s="65"/>
+      <c r="E65" s="65"/>
+      <c r="F65" s="65"/>
+      <c r="G65" s="65"/>
+      <c r="H65" s="65"/>
+      <c r="I65" s="65"/>
+      <c r="J65" s="66"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="62"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="68"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="68"/>
+      <c r="H66" s="68"/>
+      <c r="I66" s="68"/>
+      <c r="J66" s="69"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="62"/>
+      <c r="B67" s="67"/>
+      <c r="C67" s="68"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
+      <c r="H67" s="68"/>
+      <c r="I67" s="68"/>
+      <c r="J67" s="69"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="63"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
+      <c r="G68" s="71"/>
+      <c r="H68" s="71"/>
+      <c r="I68" s="71"/>
+      <c r="J68" s="72"/>
+    </row>
+    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="C69" s="55"/>
+      <c r="D69" s="55"/>
+      <c r="E69" s="55"/>
+      <c r="F69" s="55"/>
+      <c r="G69" s="55"/>
+      <c r="H69" s="55"/>
+      <c r="I69" s="55"/>
+      <c r="J69" s="56"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="60"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="58"/>
+      <c r="J70" s="59"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A57:A60"/>
-    <mergeCell ref="B57:J60"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A40:B40"/>
+  <mergeCells count="23">
+    <mergeCell ref="B69:J70"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A65:A68"/>
+    <mergeCell ref="B65:J68"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
